--- a/samples/ss_sumbagut_ingest.xlsx
+++ b/samples/ss_sumbagut_ingest.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,21 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GABUNGAN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gabungan Aceh &amp; Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>24</v>
       </c>
     </row>
@@ -721,25 +736,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -796,21 +802,16 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -849,25 +850,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -924,21 +916,16 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -977,19 +964,11 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1038,25 +1017,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1113,21 +1083,16 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1166,19 +1131,11 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1227,25 +1184,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1302,21 +1250,16 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1355,25 +1298,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1430,21 +1364,16 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1501,21 +1430,16 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1554,25 +1478,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1629,21 +1544,16 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1700,21 +1610,16 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1753,25 +1658,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1828,21 +1724,16 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1899,21 +1790,16 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -1952,25 +1838,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2027,21 +1904,16 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2098,21 +1970,16 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2151,25 +2018,16 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2226,21 +2084,16 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2297,21 +2150,16 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2350,25 +2198,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2407,27 +2246,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2466,25 +2297,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2523,25 +2345,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2580,27 +2393,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2639,27 +2444,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2698,27 +2495,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2757,25 +2546,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2814,19 +2594,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2875,25 +2647,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2932,27 +2695,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -2991,25 +2746,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3048,19 +2794,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3109,27 +2847,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3168,27 +2898,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3227,25 +2949,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3284,25 +2997,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3341,25 +3045,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3398,25 +3093,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3455,25 +3141,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3512,25 +3189,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3569,25 +3237,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3626,19 +3285,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3687,25 +3338,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3744,19 +3386,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3805,25 +3439,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3862,25 +3487,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>simbol pembangkit di Kuala Tanjung = Inalum (peta slide 25)</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3929,25 +3548,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -3986,25 +3596,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4043,27 +3644,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
         <v>1</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4102,27 +3695,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
         <v>1</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4161,25 +3746,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4218,25 +3794,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4275,25 +3842,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4332,25 +3890,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4389,25 +3938,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4446,25 +3986,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4503,27 +4034,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4562,25 +4085,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4619,25 +4133,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4676,27 +4181,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
         <v>1</v>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4735,27 +4232,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4794,31 +4283,24 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>digambar di pita Tier-1 tanpa pembangkit; hanya lewat Bireun</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4857,27 +4339,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4916,27 +4390,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -4975,27 +4441,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5034,27 +4492,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5093,21 +4543,14 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -5156,25 +4599,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5213,27 +4647,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
         <v>1</v>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5272,27 +4698,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="n">
         <v>1</v>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5331,27 +4749,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
         <v>1</v>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5390,27 +4800,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5449,27 +4851,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="n">
         <v>1</v>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5508,27 +4902,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="n">
         <v>1</v>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5567,27 +4953,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="n">
         <v>1</v>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5626,27 +5004,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
         <v>1</v>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5685,27 +5055,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
         <v>1</v>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5744,27 +5106,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
         <v>1</v>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5803,27 +5157,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
         <v>1</v>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5862,27 +5208,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
         <v>1</v>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5921,27 +5259,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
         <v>1</v>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -5980,27 +5310,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
         <v>1</v>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6039,27 +5361,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
         <v>1</v>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6098,27 +5412,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
         <v>1</v>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6157,27 +5463,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
         <v>1</v>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6216,27 +5514,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
         <v>1</v>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6275,27 +5565,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
         <v>1</v>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6334,27 +5616,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
         <v>1</v>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6393,25 +5667,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6450,27 +5715,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
         <v>1</v>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6509,27 +5766,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
         <v>1</v>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6568,27 +5817,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
         <v>1</v>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6627,27 +5868,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
         <v>1</v>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6686,27 +5919,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
         <v>1</v>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6745,27 +5970,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
         <v>1</v>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6804,27 +6021,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
         <v>1</v>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6863,27 +6072,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="n">
         <v>1</v>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6922,27 +6123,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="n">
         <v>1</v>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -6981,27 +6174,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="n">
         <v>1</v>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7040,21 +6225,14 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="n">
         <v>1</v>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -7103,21 +6281,14 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
         <v>1</v>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -7166,27 +6337,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
         <v>1</v>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7225,27 +6388,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
         <v>1</v>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7284,27 +6439,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
         <v>1</v>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7343,27 +6490,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
         <v>1</v>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7402,27 +6541,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
         <v>1</v>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7461,27 +6592,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
         <v>1</v>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7520,27 +6643,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
         <v>1</v>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7579,27 +6694,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="n">
         <v>1</v>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7638,27 +6745,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
         <v>1</v>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7697,27 +6796,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="n">
         <v>1</v>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7756,27 +6847,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
         <v>1</v>
       </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7815,27 +6898,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
         <v>1</v>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7874,27 +6949,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="n">
         <v>1</v>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7933,27 +7000,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="n">
         <v>1</v>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -7992,27 +7051,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="n">
         <v>1</v>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8051,27 +7102,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="n">
         <v>1</v>
       </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8110,25 +7153,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="n">
         <v>1</v>
       </c>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
           <t>GI taping pada SUTT Pematang Siantar - Tebing Tinggi (risiko #12)</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -8177,27 +7214,19 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="n">
         <v>1</v>
       </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8236,17 +7265,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
           <t>batas ke Subsistem Sumbagteng</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -8262,7 +7285,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8379,7 +7401,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTU Nagan Raya (275 kV)</t>
@@ -8400,7 +7421,6 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -8414,8 +7434,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8442,7 +7460,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Outlet PLTMG Arun</t>
@@ -8463,7 +7480,6 @@
           <t>275 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -8477,8 +7493,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8505,7 +7519,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Outlet PLTD Lueng Bata</t>
@@ -8526,7 +7539,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -8540,8 +7552,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8568,7 +7578,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Outlet PLTU Nagan Raya (150 kV)</t>
@@ -8589,7 +7598,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -8603,8 +7611,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8631,7 +7637,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Outlet PLTGU Belawan</t>
@@ -8652,7 +7657,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>1</v>
       </c>
@@ -8666,8 +7670,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8694,7 +7696,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Outlet PLTG Paya Pasir</t>
@@ -8715,7 +7716,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>1</v>
       </c>
@@ -8729,8 +7729,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8757,7 +7755,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Outlet PLTU Belawan</t>
@@ -8778,7 +7775,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -8792,8 +7788,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8820,7 +7814,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Outlet PLTA Renun</t>
@@ -8841,7 +7834,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>1</v>
       </c>
@@ -8855,8 +7847,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8883,7 +7873,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Outlet PLTA Wampu</t>
@@ -8904,7 +7893,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -8918,8 +7906,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -8946,7 +7932,6 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Outlet PLTP Sarulla NIL</t>
@@ -8967,7 +7952,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -8981,8 +7965,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9009,7 +7991,6 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Outlet PLTP Sarulla SIL</t>
@@ -9030,7 +8011,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>1</v>
       </c>
@@ -9044,8 +8024,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9072,7 +8050,6 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Outlet Inalum</t>
@@ -9093,7 +8070,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>1</v>
       </c>
@@ -9107,8 +8083,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9135,7 +8109,6 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Outlet PLTA Hasang</t>
@@ -9156,7 +8129,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>1</v>
       </c>
@@ -9170,8 +8142,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9198,7 +8168,6 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Outlet PLTA Sipan 1</t>
@@ -9219,7 +8188,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1</v>
       </c>
@@ -9233,8 +8201,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9261,7 +8227,6 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Outlet PLTA Sipan 2</t>
@@ -9282,7 +8247,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1</v>
       </c>
@@ -9296,8 +8260,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9324,7 +8286,6 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Outlet PLTU Labuhan Angin</t>
@@ -9345,7 +8306,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>1</v>
       </c>
@@ -9359,8 +8319,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9387,7 +8345,6 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Outlet PLTP Sorik Marapi</t>
@@ -9408,7 +8365,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>1</v>
       </c>
@@ -9422,8 +8378,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9450,7 +8404,6 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Outlet pembangkit Titi Kuning</t>
@@ -9471,7 +8424,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>1</v>
       </c>
@@ -9485,8 +8437,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9513,7 +8463,6 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Outlet pembangkit Glugur</t>
@@ -9534,7 +8483,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>1</v>
       </c>
@@ -9548,8 +8496,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9576,7 +8522,6 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>SUTT 150 kV Banda Aceh - Ulee Kareng</t>
@@ -9597,7 +8542,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -9611,8 +8555,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9639,7 +8581,6 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>SUTT 150 kV Ulee Kareng - Krueng Raya</t>
@@ -9660,7 +8601,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -9674,8 +8614,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9702,7 +8640,6 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTT 150 kV Banda Aceh - Jantho</t>
@@ -9723,7 +8660,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -9737,8 +8673,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9765,7 +8699,6 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>SUTT 150 kV Banda Aceh - Sigli</t>
@@ -9786,7 +8719,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>1</v>
       </c>
@@ -9800,8 +8732,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9828,7 +8758,6 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sigli - Jantho</t>
@@ -9849,7 +8778,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>1</v>
       </c>
@@ -9863,8 +8791,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9891,7 +8817,6 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>SUTT 150 kV Nagan Raya - Meulaboh</t>
@@ -9912,7 +8837,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -9926,8 +8850,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -9954,7 +8876,6 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>SUTT 150 kV Meulaboh - Tapak Tuan</t>
@@ -9975,7 +8896,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -9989,8 +8909,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10017,7 +8935,6 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>SUTT 150 kV Nagan Raya - Blang Pidie</t>
@@ -10038,7 +8955,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -10052,8 +8968,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10105,7 +9019,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>1</v>
       </c>
@@ -10119,8 +9032,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10172,7 +9083,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>1</v>
       </c>
@@ -10186,8 +9096,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10239,7 +9147,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>1</v>
       </c>
@@ -10253,8 +9160,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10306,7 +9211,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -10320,8 +9224,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10348,7 +9250,6 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>SUTT 150 kV Peusangan - Bireun</t>
@@ -10369,7 +9270,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -10383,8 +9283,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10411,7 +9309,6 @@
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>SUTT 150 kV Peusangan - Takengon</t>
@@ -10432,7 +9329,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -10446,8 +9342,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10499,7 +9393,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -10513,8 +9406,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10566,7 +9457,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>1</v>
       </c>
@@ -10580,8 +9470,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10633,7 +9521,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>1</v>
       </c>
@@ -10647,8 +9534,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10700,7 +9585,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>1</v>
       </c>
@@ -10714,8 +9598,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10767,7 +9649,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>1</v>
       </c>
@@ -10781,8 +9662,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10809,7 +9688,6 @@
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>SUTT 150 kV Langsa - Tualang Cut</t>
@@ -10830,7 +9708,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -10844,8 +9721,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10897,7 +9772,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>2</v>
       </c>
@@ -10911,8 +9785,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -10964,7 +9836,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>1</v>
       </c>
@@ -10978,8 +9849,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11006,7 +9875,6 @@
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>SUTT 150 kV Pangkalan Brandan - Tanjung Pura</t>
@@ -11027,7 +9895,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>1</v>
       </c>
@@ -11041,8 +9908,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11069,7 +9934,6 @@
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>SUTT 150 kV Binjai - Tanjung Pura</t>
@@ -11090,7 +9954,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>1</v>
       </c>
@@ -11104,8 +9967,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11132,7 +9993,6 @@
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>SUTT 150 kV Binjai - Paya Geli</t>
@@ -11153,7 +10013,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -11167,8 +10026,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11195,7 +10052,6 @@
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>SUTT 150 kV Binjai - Belawan CC</t>
@@ -11216,7 +10072,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>2</v>
       </c>
@@ -11230,8 +10085,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11258,7 +10111,6 @@
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>SUTT 150 kV Belawan CC - Sei Rotan</t>
@@ -11279,7 +10131,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -11293,8 +10144,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11321,7 +10170,6 @@
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sei Rotan - Titi Kuning</t>
@@ -11342,7 +10190,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>2</v>
       </c>
@@ -11356,8 +10203,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11384,7 +10229,6 @@
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>SUTT 150 kV Titi Kuning - Brastagi</t>
@@ -11405,7 +10249,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -11419,8 +10262,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11447,7 +10288,6 @@
       <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>SUTT 150 kV Paya Pasir - Paya Geli</t>
@@ -11468,7 +10308,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>2</v>
       </c>
@@ -11482,8 +10321,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11535,7 +10372,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>2</v>
       </c>
@@ -11549,8 +10385,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11577,7 +10411,6 @@
       <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>SUTT 150 kV Paya Pasir - Belawan PLTU</t>
@@ -11598,7 +10431,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>2</v>
       </c>
@@ -11612,8 +10444,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11640,7 +10470,6 @@
       <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>SUTT 150 kV Paya Pasir - Sei Rotan</t>
@@ -11661,7 +10490,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>2</v>
       </c>
@@ -11675,8 +10503,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11728,7 +10554,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>2</v>
       </c>
@@ -11742,8 +10567,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11770,7 +10593,6 @@
       <c r="A55" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sei Rotan - Denai</t>
@@ -11791,7 +10613,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>1</v>
       </c>
@@ -11805,8 +10626,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11833,7 +10652,6 @@
       <c r="A56" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>SUTT 150 kV Denai - Tamora</t>
@@ -11854,7 +10672,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>1</v>
       </c>
@@ -11868,8 +10685,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11896,7 +10711,6 @@
       <c r="A57" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>SUTT 150 kV Tamora - Kualanamu</t>
@@ -11917,7 +10731,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>2</v>
       </c>
@@ -11931,8 +10744,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -11959,7 +10770,6 @@
       <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sei Rotan - Tamora</t>
@@ -11980,7 +10790,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>1</v>
       </c>
@@ -11994,8 +10803,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12022,7 +10829,6 @@
       <c r="A59" t="n">
         <v>58</v>
       </c>
-      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sei Rotan - Perbaungan</t>
@@ -12043,7 +10849,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>1</v>
       </c>
@@ -12057,8 +10862,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12110,7 +10913,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>1</v>
       </c>
@@ -12124,8 +10926,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12152,7 +10952,6 @@
       <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sei Rotan - Tebing Tinggi</t>
@@ -12173,7 +10972,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>1</v>
       </c>
@@ -12187,8 +10985,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12215,7 +11011,6 @@
       <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>SUTT 150 kV Perbaungan - Kualanamu</t>
@@ -12236,7 +11031,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>2</v>
       </c>
@@ -12250,8 +11044,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12278,7 +11070,6 @@
       <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>SUTT 150 kV Belawan PLTU - Labuhan</t>
@@ -12299,7 +11090,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>1</v>
       </c>
@@ -12313,8 +11103,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12341,7 +11129,6 @@
       <c r="A64" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>SUTT 150 kV Labuhan - Lamhotma</t>
@@ -12362,7 +11149,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>1</v>
       </c>
@@ -12376,8 +11162,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12404,7 +11188,6 @@
       <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>SUTT 150 kV Lamhotma - Belawan PLTU</t>
@@ -12425,7 +11208,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>1</v>
       </c>
@@ -12439,8 +11221,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12492,7 +11272,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>2</v>
       </c>
@@ -12506,8 +11285,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12534,7 +11311,6 @@
       <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>SUTT 150 kV Paya Geli - Selayang</t>
@@ -12555,7 +11331,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>2</v>
       </c>
@@ -12569,8 +11344,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12597,7 +11370,6 @@
       <c r="A68" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>SUTT 150 kV Selayang - Namorambe</t>
@@ -12618,7 +11390,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>2</v>
       </c>
@@ -12632,8 +11403,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12660,7 +11429,6 @@
       <c r="A69" t="n">
         <v>68</v>
       </c>
-      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>SUTT 150 kV Titi Kuning - Namorambe</t>
@@ -12681,7 +11449,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>2</v>
       </c>
@@ -12695,8 +11462,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12748,7 +11513,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>2</v>
       </c>
@@ -12762,8 +11526,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12790,7 +11552,6 @@
       <c r="A71" t="n">
         <v>70</v>
       </c>
-      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>SUTT 150 kV Namorambe - Galang</t>
@@ -12811,7 +11572,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>2</v>
       </c>
@@ -12825,8 +11585,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12853,7 +11611,6 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>SUTT 150 kV Galang - Tamora</t>
@@ -12874,7 +11631,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>2</v>
       </c>
@@ -12888,8 +11644,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12916,7 +11670,6 @@
       <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>SUTT 150 kV Tamora - Negeri Dolok</t>
@@ -12937,7 +11690,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>1</v>
       </c>
@@ -12951,8 +11703,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -12979,7 +11729,6 @@
       <c r="A74" t="n">
         <v>73</v>
       </c>
-      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>SUTT 150 kV Galang - Negeri Dolok</t>
@@ -13000,7 +11749,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>1</v>
       </c>
@@ -13014,8 +11762,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13042,7 +11788,6 @@
       <c r="A75" t="n">
         <v>74</v>
       </c>
-      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>SUTT 150 kV Simangkuk - Porsea</t>
@@ -13063,7 +11808,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>2</v>
       </c>
@@ -13077,8 +11821,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13105,7 +11847,6 @@
       <c r="A76" t="n">
         <v>75</v>
       </c>
-      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>SUTT 150 kV Porsea - Tarutung</t>
@@ -13126,7 +11867,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>2</v>
       </c>
@@ -13140,8 +11880,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13168,7 +11906,6 @@
       <c r="A77" t="n">
         <v>76</v>
       </c>
-      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>SUTT 150 kV Tarutung - Sibolga</t>
@@ -13189,7 +11926,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -13203,8 +11939,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13231,7 +11965,6 @@
       <c r="A78" t="n">
         <v>77</v>
       </c>
-      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>SUTT 150 kV Porsea - Pematang Siantar</t>
@@ -13252,7 +11985,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -13266,8 +11998,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13294,7 +12024,6 @@
       <c r="A79" t="n">
         <v>78</v>
       </c>
-      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>SUTT 150 kV Pematang Siantar - Tanah Jawa</t>
@@ -13315,7 +12044,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>2</v>
       </c>
@@ -13329,8 +12057,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13357,7 +12083,6 @@
       <c r="A80" t="n">
         <v>79</v>
       </c>
-      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>SUTT 150 kV Pematang Siantar - Tebing Tinggi</t>
@@ -13378,7 +12103,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>1</v>
       </c>
@@ -13392,8 +12116,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13445,7 +12167,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>1</v>
       </c>
@@ -13459,8 +12180,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13487,7 +12206,6 @@
       <c r="A82" t="n">
         <v>81</v>
       </c>
-      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
           <t>SUTT 150 kV Dolok Sanggul - Tarutung</t>
@@ -13508,7 +12226,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>1</v>
       </c>
@@ -13522,8 +12239,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13550,7 +12265,6 @@
       <c r="A83" t="n">
         <v>82</v>
       </c>
-      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>SUTT 150 kV Tarutung - Tele</t>
@@ -13571,7 +12285,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>1</v>
       </c>
@@ -13585,8 +12298,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13613,7 +12324,6 @@
       <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
           <t>SUTT 150 kV Dolok Sanggul - Sidikalang</t>
@@ -13634,7 +12344,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>1</v>
       </c>
@@ -13648,8 +12357,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13676,7 +12383,6 @@
       <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sidikalang - Tele</t>
@@ -13697,7 +12403,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>1</v>
       </c>
@@ -13711,8 +12416,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13739,7 +12442,6 @@
       <c r="A86" t="n">
         <v>85</v>
       </c>
-      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
           <t>SUTT 150 kV Tele - Pangururan</t>
@@ -13760,7 +12462,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -13774,8 +12475,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13802,7 +12501,6 @@
       <c r="A87" t="n">
         <v>86</v>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>SUTT 150 kV PLTA Renun - Sidikalang</t>
@@ -13823,7 +12521,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -13837,8 +12534,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13865,7 +12560,6 @@
       <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sidikalang - Siempat Rube</t>
@@ -13886,7 +12580,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>2</v>
       </c>
@@ -13900,8 +12593,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -13953,7 +12644,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>2</v>
       </c>
@@ -13967,8 +12657,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14020,7 +12708,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -14034,8 +12721,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14062,7 +12747,6 @@
       <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
           <t>SUTT 150 kV PLTA Wampu - Brastagi</t>
@@ -14083,7 +12767,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -14097,8 +12780,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14125,7 +12806,6 @@
       <c r="A92" t="n">
         <v>91</v>
       </c>
-      <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
           <t>SUTT 150 kV Brastagi - Kutacane</t>
@@ -14146,7 +12826,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -14160,8 +12839,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14188,7 +12865,6 @@
       <c r="A93" t="n">
         <v>92</v>
       </c>
-      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sarulla - PLTP NIL</t>
@@ -14209,7 +12885,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -14223,8 +12898,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14251,7 +12924,6 @@
       <c r="A94" t="n">
         <v>93</v>
       </c>
-      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sarulla - PLTP SIL</t>
@@ -14272,7 +12944,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -14286,8 +12957,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14314,7 +12983,6 @@
       <c r="A95" t="n">
         <v>94</v>
       </c>
-      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
           <t>SUTT 150 kV Kuala Tanjung - Tebing Tinggi</t>
@@ -14335,7 +13003,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>2</v>
       </c>
@@ -14349,8 +13016,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14377,7 +13042,6 @@
       <c r="A96" t="n">
         <v>95</v>
       </c>
-      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
           <t>SUTT 150 kV Kuala Tanjung - Sei Mangke</t>
@@ -14398,7 +13062,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -14412,8 +13075,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14440,7 +13101,6 @@
       <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sei Mangke - Kisaran</t>
@@ -14461,7 +13121,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -14475,8 +13134,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14503,7 +13160,6 @@
       <c r="A98" t="n">
         <v>97</v>
       </c>
-      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
           <t>SUTT 150 kV Kisaran - Tanjung Balai</t>
@@ -14524,7 +13180,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>2</v>
       </c>
@@ -14538,8 +13193,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14566,7 +13219,6 @@
       <c r="A99" t="n">
         <v>98</v>
       </c>
-      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
           <t>SUTT 150 kV Kisaran - Aek Kanopan</t>
@@ -14587,7 +13239,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>1</v>
       </c>
@@ -14601,8 +13252,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14629,7 +13278,6 @@
       <c r="A100" t="n">
         <v>99</v>
       </c>
-      <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
           <t>SUTT 150 kV Aek Kanopan - PLTA Hasang</t>
@@ -14650,7 +13298,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>1</v>
       </c>
@@ -14664,8 +13311,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14692,7 +13337,6 @@
       <c r="A101" t="n">
         <v>100</v>
       </c>
-      <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
           <t>SUTT 150 kV PLTA Hasang - Rantau Prapat</t>
@@ -14713,7 +13357,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>1</v>
       </c>
@@ -14727,8 +13370,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14755,7 +13396,6 @@
       <c r="A102" t="n">
         <v>101</v>
       </c>
-      <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
           <t>SUTT 150 kV Kisaran - Rantau Prapat</t>
@@ -14776,7 +13416,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>1</v>
       </c>
@@ -14790,8 +13429,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14818,7 +13455,6 @@
       <c r="A103" t="n">
         <v>102</v>
       </c>
-      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
           <t>SUTT 150 kV Rantau Prapat - Labuhan Bilik</t>
@@ -14839,7 +13475,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -14853,8 +13488,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14881,7 +13514,6 @@
       <c r="A104" t="n">
         <v>103</v>
       </c>
-      <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
           <t>SUTT 150 kV Rantau Prapat - Gunung Tua</t>
@@ -14902,7 +13534,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>1</v>
       </c>
@@ -14916,8 +13547,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -14944,7 +13573,6 @@
       <c r="A105" t="n">
         <v>104</v>
       </c>
-      <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
           <t>SUTT 150 kV Rantau Prapat - Padang Sidempuan</t>
@@ -14965,7 +13593,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>1</v>
       </c>
@@ -14979,8 +13606,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15007,7 +13632,6 @@
       <c r="A106" t="n">
         <v>105</v>
       </c>
-      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
           <t>SUTT 150 kV Padang Sidempuan - Gunung Tua</t>
@@ -15028,7 +13652,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>1</v>
       </c>
@@ -15042,8 +13665,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15070,7 +13691,6 @@
       <c r="A107" t="n">
         <v>106</v>
       </c>
-      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
           <t>SUTT 150 kV Rantau Prapat - Kota Pinang</t>
@@ -15091,7 +13711,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>1</v>
       </c>
@@ -15105,8 +13724,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15133,7 +13750,6 @@
       <c r="A108" t="n">
         <v>107</v>
       </c>
-      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
           <t>SUTT 150 kV Kota Pinang - Bagan Batu (arah Sumbagteng)</t>
@@ -15154,7 +13770,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>1</v>
       </c>
@@ -15168,8 +13783,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15196,7 +13809,6 @@
       <c r="A109" t="n">
         <v>108</v>
       </c>
-      <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
           <t>SUTT 150 kV Gunung Tua - Sibuhuan</t>
@@ -15217,7 +13829,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>2</v>
       </c>
@@ -15231,8 +13842,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15284,7 +13893,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>1</v>
       </c>
@@ -15298,8 +13906,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15351,7 +13957,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>1</v>
       </c>
@@ -15365,8 +13970,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15418,7 +14021,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>1</v>
       </c>
@@ -15432,8 +14034,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15485,7 +14085,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -15499,8 +14098,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15527,7 +14124,6 @@
       <c r="A114" t="n">
         <v>113</v>
       </c>
-      <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
           <t>SUTT 150 kV Sibolga - Martabe</t>
@@ -15548,7 +14144,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -15562,8 +14157,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15590,7 +14183,6 @@
       <c r="A115" t="n">
         <v>114</v>
       </c>
-      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
           <t>SUTT 150 kV Padang Sidempuan - Martabe</t>
@@ -15611,7 +14203,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -15625,8 +14216,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15653,7 +14242,6 @@
       <c r="A116" t="n">
         <v>115</v>
       </c>
-      <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
           <t>SUTT 150 kV New Padang Sidempuan - Padang Sidempuan</t>
@@ -15674,7 +14262,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -15688,8 +14275,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15741,7 +14326,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -15755,8 +14339,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15783,7 +14365,6 @@
       <c r="A118" t="n">
         <v>117</v>
       </c>
-      <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>SUTT 150 kV PLTP Sorik Marapi - Panyabungan</t>
@@ -15804,7 +14385,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -15818,8 +14398,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
           <t>Sumbagut</t>
@@ -15993,7 +14571,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>SUMUT</t>
@@ -16037,7 +14614,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>SUMUT</t>
